--- a/diseases/d042/2015-2019.xlsx
+++ b/diseases/d042/2015-2019.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2191,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2780,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.001961403059472987</v>
       </c>
@@ -3381,9 +3369,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3958,6 @@
       <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.001961403059472987</v>
       </c>
@@ -4565,9 +4547,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5157,9 +5136,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5749,9 +5725,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6341,9 +6314,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6903,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7525,9 +7492,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8117,9 +8081,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8857,9 +8818,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9253,9 +9211,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9993,9 +9948,6 @@
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -10733,9 +10685,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -11473,9 +11422,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12213,9 +12159,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12953,9 +12896,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13693,9 +13633,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14433,9 +14370,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -15173,9 +15107,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15913,9 +15844,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16653,9 +16581,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17393,9 +17318,6 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -17985,9 +17907,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18381,9 +18300,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18973,9 +18889,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -19565,9 +19478,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20157,9 +20067,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20749,9 +20656,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21341,9 +21245,6 @@
       <c r="O139" t="n">
         <v>2</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.003884530731352934</v>
       </c>
@@ -21933,9 +21834,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22525,9 +22423,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -23117,9 +23012,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -23709,9 +23601,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -24301,9 +24190,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -24893,9 +24779,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25633,9 +25516,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -26029,9 +25909,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26769,9 +26646,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -27509,9 +27383,6 @@
       <c r="O180" t="n">
         <v>1</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -28249,9 +28120,6 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -28989,9 +28857,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -29729,9 +29594,6 @@
       <c r="O195" t="n">
         <v>2</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.00387289964422382</v>
       </c>
@@ -30469,9 +30331,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -31209,9 +31068,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -31949,9 +31805,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -32689,9 +32542,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -33429,9 +33279,6 @@
       <c r="O220" t="n">
         <v>1</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -34169,9 +34016,6 @@
       <c r="O225" t="n">
         <v>1</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -34909,9 +34753,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -35305,9 +35146,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -36341,9 +36179,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -37081,9 +36916,6 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -37821,9 +37653,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -38561,9 +38390,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -39597,9 +39423,6 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -40485,9 +40308,6 @@
       <c r="O267" t="n">
         <v>1</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -41225,9 +41045,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -41965,9 +41782,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -42853,9 +42667,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -43741,9 +43552,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -44627,9 +44435,6 @@
         <v>0</v>
       </c>
       <c r="O295" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q295" t="n">
         <v>0</v>
       </c>
       <c r="R295" t="n">
